--- a/output/2026-10-03_14_Malesia_Perlis_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-10-03_14_Malesia_Perlis_Depolverazione_Trattamento_aria.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rivenditore multi-brand di utensili/hardware con categoria dedicata 'Fans &amp; Ventilation': distribuisce fan/blower industriali e accessori per aspirazione (dust hose). Non e' uno specialista esclusivo di depolverazione ma rivenditore B2B di attrezzature di ventilazione/aspirazione. Verificato via sito ufficiale e ricerche indipendenti.</t>
+          <t>Rivenditore multi-brand di utensili/hardware con categoria dedicata 'Fans &amp; Ventilation': distribuisce fan/blower industriali e accessori per aspirazione (dust hose). Non e' uno specialista esclusivo di depolverazione ma rivenditore B2B di attrezzature di ventilazione/aspirazione. Verificato via sito ufficiale e ricerche indipendenti. [DUPLICATO — vedi anche: 2026-10-02_19_Malesia_Negeri_Sembilan_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Produttore e distributore autorizzato di bag filter dust collector, packed tower scrubber, cicloni, precipitatori elettrostatici, filtri a carbone attivo; distribuisce i brand DUCLEAN, Absolent, 3NINE e DELFIN (vacuum industriali). Distributore B2B riconosciuto del settore air pollution control in Malesia. Verificato via sito ufficiale (fetch diretto).</t>
+          <t>Produttore e distributore autorizzato di bag filter dust collector, packed tower scrubber, cicloni, precipitatori elettrostatici, filtri a carbone attivo; distribuisce i brand DUCLEAN, Absolent, 3NINE e DELFIN (vacuum industriali). Distributore B2B riconosciuto del settore air pollution control in Malesia. Verificato via sito ufficiale (fetch diretto). [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -590,7 +590,6 @@
           <t>Kemac Sdn Bhd</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Kuala Lumpur - sede fuori Perlis; copertura nazionale presunta (azienda storica dal 1978)</t>
@@ -601,11 +600,9 @@
           <t>Depolverazione / Trattamento aria</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Produttore storico (incorporata nel 1978, SSM 039807-W) di bag filter dust collector e sistemi di raccolta/movimentazione/trasporto polveri per controllo inquinamento industriale. Nessun sito web ufficiale individuato; telefono ed email non reperibili pubblicamente nelle fonti consultate (EMIS, directory aziendali) - lasciati vuoti per non inventare dati.</t>
+          <t>Produttore storico (incorporata nel 1978, SSM 039807-W) di bag filter dust collector e sistemi di raccolta/movimentazione/trasporto polveri per controllo inquinamento industriale. Nessun sito web ufficiale individuato; telefono ed email non reperibili pubblicamente nelle fonti consultate (EMIS, directory aziendali) - lasciati vuoti per non inventare dati. [DUPLICATO — vedi anche: 2026-10-01_07_Malesia_Kelantan_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -620,7 +617,6 @@
           <t>Dust Cone Hopper Systems Sdn Bhd</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
           <t>Selangor (Petaling Jaya, Jaya One) - sede fuori Perlis; opera su mercati internazionali (porti/terminal)</t>
@@ -636,7 +632,6 @@
           <t>6011-16664030</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Produttore di sistemi meccanici passivi di soppressione/contenimento polvere (hopper) per bulk material handling (grano, fertilizzanti, minerali) in applicazioni di shiploading, truck loading, scarico silo. Verificato via directory di settore (Bulkinside, SGPGrid) e ricerche indipendenti; email non reperibile pubblicamente.</t>
@@ -644,7 +639,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -686,7 +681,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -716,7 +711,6 @@
           <t>+603 8961 2908</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Produttore di filtrazione aria (HEPA, filtri particellari), attrezzature cleanroom, fan filter unit (FFU), raised floor. Azienda consolidata (dal 2001), parte di gruppo internazionale con presenza in Cina. Email non riportata in chiaro nelle fonti consultate (oscurata) - lasciata vuota per non inventare dati. Verificato via directory aziendali (AFS Society, Craft, Hiredly).</t>
@@ -724,7 +718,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
